--- a/storage/templates/Bar_Salon.xlsx
+++ b/storage/templates/Bar_Salon.xlsx
@@ -736,7 +736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AN195"/>
+  <dimension ref="A1:AN198"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="10.77734375" customWidth="1" style="1" min="1" max="1"/>
@@ -13797,40 +13797,247 @@
         <v/>
       </c>
     </row>
-    <row r="194" ht="22.05" customHeight="1">
-      <c r="C194" s="8">
-        <f>SUM(C7:C193)</f>
-        <v/>
-      </c>
-      <c r="E194" s="11" t="inlineStr">
+    <row r="194" ht="25.05" customHeight="1">
+      <c r="A194" s="35" t="inlineStr">
+        <is>
+          <t>2132</t>
+        </is>
+      </c>
+      <c r="B194" s="4" t="inlineStr">
+        <is>
+          <t>VINO GEN CHICLANERO 16 LT</t>
+        </is>
+      </c>
+      <c r="C194" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D194" s="9" t="inlineStr">
+        <is>
+          <t>LITRO</t>
+        </is>
+      </c>
+      <c r="E194" s="10" t="n">
+        <v>4.56444</v>
+      </c>
+      <c r="F194" s="13">
+        <f>C194*E194</f>
+        <v/>
+      </c>
+      <c r="G194" s="20" t="n"/>
+      <c r="H194" s="20" t="n"/>
+      <c r="I194" s="20" t="n"/>
+      <c r="J194" s="20" t="n"/>
+      <c r="K194" s="20" t="n"/>
+      <c r="L194" s="20" t="n"/>
+      <c r="M194" s="20" t="n"/>
+      <c r="N194" s="20" t="n"/>
+      <c r="O194" s="20" t="n"/>
+      <c r="P194" s="20" t="n"/>
+      <c r="Q194" s="20" t="n"/>
+      <c r="R194" s="20" t="n"/>
+      <c r="S194" s="20" t="n"/>
+      <c r="T194" s="20" t="n"/>
+      <c r="U194" s="20" t="n"/>
+      <c r="V194" s="20" t="n"/>
+      <c r="W194" s="20" t="n"/>
+      <c r="X194" s="20" t="n"/>
+      <c r="Y194" s="20" t="n"/>
+      <c r="Z194" s="20" t="n"/>
+      <c r="AA194" s="20" t="n"/>
+      <c r="AB194" s="20" t="n"/>
+      <c r="AC194" s="20" t="n"/>
+      <c r="AD194" s="20" t="n"/>
+      <c r="AE194" s="20" t="n"/>
+      <c r="AF194" s="20" t="n"/>
+      <c r="AG194" s="20" t="n"/>
+      <c r="AH194" s="20" t="n"/>
+      <c r="AI194" s="20" t="n"/>
+      <c r="AJ194" s="20" t="n"/>
+      <c r="AK194" s="20" t="n"/>
+      <c r="AL194" s="21">
+        <f>SUM(G194:AK194)</f>
+        <v/>
+      </c>
+      <c r="AM194" s="22">
+        <f>SUM(C194,AL194)</f>
+        <v/>
+      </c>
+      <c r="AN194" s="23">
+        <f>E194*AM194</f>
+        <v/>
+      </c>
+    </row>
+    <row r="195" ht="25.05" customHeight="1">
+      <c r="A195" s="35" t="inlineStr">
+        <is>
+          <t>4989</t>
+        </is>
+      </c>
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t>VINO GEN FINO OLOROSO GRANEL</t>
+        </is>
+      </c>
+      <c r="C195" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D195" s="9" t="inlineStr">
+        <is>
+          <t>LITRO</t>
+        </is>
+      </c>
+      <c r="E195" s="10" t="n">
+        <v>4.71986</v>
+      </c>
+      <c r="F195" s="13">
+        <f>C195*E195</f>
+        <v/>
+      </c>
+      <c r="G195" s="20" t="n"/>
+      <c r="H195" s="20" t="n"/>
+      <c r="I195" s="20" t="n"/>
+      <c r="J195" s="20" t="n"/>
+      <c r="K195" s="20" t="n"/>
+      <c r="L195" s="20" t="n"/>
+      <c r="M195" s="20" t="n"/>
+      <c r="N195" s="20" t="n"/>
+      <c r="O195" s="20" t="n"/>
+      <c r="P195" s="20" t="n"/>
+      <c r="Q195" s="20" t="n"/>
+      <c r="R195" s="20" t="n"/>
+      <c r="S195" s="20" t="n"/>
+      <c r="T195" s="20" t="n"/>
+      <c r="U195" s="20" t="n"/>
+      <c r="V195" s="20" t="n"/>
+      <c r="W195" s="20" t="n"/>
+      <c r="X195" s="20" t="n"/>
+      <c r="Y195" s="20" t="n"/>
+      <c r="Z195" s="20" t="n"/>
+      <c r="AA195" s="20" t="n"/>
+      <c r="AB195" s="20" t="n"/>
+      <c r="AC195" s="20" t="n"/>
+      <c r="AD195" s="20" t="n"/>
+      <c r="AE195" s="20" t="n"/>
+      <c r="AF195" s="20" t="n"/>
+      <c r="AG195" s="20" t="n"/>
+      <c r="AH195" s="20" t="n"/>
+      <c r="AI195" s="20" t="n"/>
+      <c r="AJ195" s="20" t="n"/>
+      <c r="AK195" s="20" t="n"/>
+      <c r="AL195" s="21">
+        <f>SUM(G195:AK195)</f>
+        <v/>
+      </c>
+      <c r="AM195" s="22">
+        <f>SUM(C195,AL195)</f>
+        <v/>
+      </c>
+      <c r="AN195" s="23">
+        <f>E195*AM195</f>
+        <v/>
+      </c>
+    </row>
+    <row r="196" ht="25.05" customHeight="1">
+      <c r="A196" s="35" t="inlineStr">
+        <is>
+          <t>25109</t>
+        </is>
+      </c>
+      <c r="B196" s="4" t="inlineStr">
+        <is>
+          <t>CHAMPAN ABELE 1757 BRUT 37.5 CL</t>
+        </is>
+      </c>
+      <c r="C196" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D196" s="9" t="inlineStr">
+        <is>
+          <t>BOTELLA</t>
+        </is>
+      </c>
+      <c r="E196" s="10" t="n">
+        <v>20.98</v>
+      </c>
+      <c r="F196" s="13">
+        <f>C196*E196</f>
+        <v/>
+      </c>
+      <c r="G196" s="20" t="n"/>
+      <c r="H196" s="20" t="n"/>
+      <c r="I196" s="20" t="n"/>
+      <c r="J196" s="20" t="n"/>
+      <c r="K196" s="20" t="n"/>
+      <c r="L196" s="20" t="n"/>
+      <c r="M196" s="20" t="n"/>
+      <c r="N196" s="20" t="n"/>
+      <c r="O196" s="20" t="n"/>
+      <c r="P196" s="20" t="n"/>
+      <c r="Q196" s="20" t="n"/>
+      <c r="R196" s="20" t="n"/>
+      <c r="S196" s="20" t="n"/>
+      <c r="T196" s="20" t="n"/>
+      <c r="U196" s="20" t="n"/>
+      <c r="V196" s="20" t="n"/>
+      <c r="W196" s="20" t="n"/>
+      <c r="X196" s="20" t="n"/>
+      <c r="Y196" s="20" t="n"/>
+      <c r="Z196" s="20" t="n"/>
+      <c r="AA196" s="20" t="n"/>
+      <c r="AB196" s="20" t="n"/>
+      <c r="AC196" s="20" t="n"/>
+      <c r="AD196" s="20" t="n"/>
+      <c r="AE196" s="20" t="n"/>
+      <c r="AF196" s="20" t="n"/>
+      <c r="AG196" s="20" t="n"/>
+      <c r="AH196" s="20" t="n"/>
+      <c r="AI196" s="20" t="n"/>
+      <c r="AJ196" s="20" t="n"/>
+      <c r="AK196" s="20" t="n"/>
+      <c r="AL196" s="21">
+        <f>SUM(G196:AK196)</f>
+        <v/>
+      </c>
+      <c r="AM196" s="22">
+        <f>SUM(C196,AL196)</f>
+        <v/>
+      </c>
+      <c r="AN196" s="23">
+        <f>E196*AM196</f>
+        <v/>
+      </c>
+    </row>
+    <row r="197" ht="22.05" customHeight="1">
+      <c r="C197" s="8">
+        <f>SUM(C7:C196)</f>
+        <v/>
+      </c>
+      <c r="E197" s="11" t="inlineStr">
         <is>
           <t>ESTOCAJE  INICIAL</t>
         </is>
       </c>
-      <c r="F194" s="12">
-        <f>SUM(F7:F193)</f>
-        <v/>
-      </c>
-      <c r="AL194" s="8">
-        <f>SUM(AL7:AL193)</f>
-        <v/>
-      </c>
-      <c r="AM194" s="8">
-        <f>SUM(AM7:AM193)</f>
-        <v/>
-      </c>
-      <c r="AN194" s="24">
-        <f>SUM(AN7:AN193)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="195" ht="22.05" customHeight="1">
-      <c r="E195" s="4" t="n"/>
-      <c r="F195" s="4" t="n"/>
-    </row>
-    <row r="196" ht="22.05" customHeight="1"/>
-    <row r="197" ht="22.05" customHeight="1"/>
-    <row r="198" ht="22.05" customHeight="1"/>
+      <c r="F197" s="12">
+        <f>SUM(F7:F196)</f>
+        <v/>
+      </c>
+      <c r="AL197" s="8">
+        <f>SUM(AL7:AL196)</f>
+        <v/>
+      </c>
+      <c r="AM197" s="8">
+        <f>SUM(AM7:AM196)</f>
+        <v/>
+      </c>
+      <c r="AN197" s="24">
+        <f>SUM(AN7:AN196)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198" ht="22.05" customHeight="1">
+      <c r="E198" s="4" t="n"/>
+      <c r="F198" s="4" t="n"/>
+    </row>
     <row r="199" ht="22.05" customHeight="1"/>
     <row r="200" ht="22.05" customHeight="1"/>
     <row r="201" ht="22.05" customHeight="1"/>
